--- a/src/Verify.OpenXml.Tests/Samples.HiddenRow.verified.xlsx
+++ b/src/Verify.OpenXml.Tests/Samples.HiddenRow.verified.xlsx
@@ -113,17 +113,17 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <name val="Aptos"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="Aptos"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="Aptos"/>
       <family val="2"/>
     </font>
   </fonts>
